--- a/diseases/d092/1995-1999.xlsx
+++ b/diseases/d092/1995-1999.xlsx
@@ -21640,7 +21640,7 @@
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -21879,7 +21879,7 @@
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -21889,7 +21889,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -22918,7 +22918,7 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -23957,7 +23957,7 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -26035,7 +26035,7 @@
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
@@ -26045,7 +26045,7 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -27074,7 +27074,7 @@
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT132" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -29152,7 +29152,7 @@
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
@@ -29162,7 +29162,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -30191,7 +30191,7 @@
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
@@ -30201,7 +30201,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -31230,7 +31230,7 @@
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
@@ -31240,7 +31240,7 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT152" t="n">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
@@ -32279,7 +32279,7 @@
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT157" t="n">
@@ -33308,7 +33308,7 @@
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
@@ -33318,7 +33318,7 @@
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT162" t="n">
@@ -34737,7 +34737,7 @@
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
@@ -34747,7 +34747,7 @@
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT169" t="n">
@@ -34976,7 +34976,7 @@
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT170" t="n">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
@@ -36025,7 +36025,7 @@
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT175" t="n">
@@ -37054,7 +37054,7 @@
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
@@ -37064,7 +37064,7 @@
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT180" t="n">
@@ -38093,7 +38093,7 @@
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT185" t="n">
@@ -39132,7 +39132,7 @@
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
@@ -39142,7 +39142,7 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT190" t="n">
@@ -40171,7 +40171,7 @@
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
@@ -40181,7 +40181,7 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT195" t="n">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
@@ -41220,7 +41220,7 @@
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT200" t="n">
@@ -42249,7 +42249,7 @@
       </c>
       <c r="AQ205" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR205" t="inlineStr">
@@ -42259,7 +42259,7 @@
       </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT205" t="n">
@@ -43288,7 +43288,7 @@
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR210" t="inlineStr">
@@ -43298,7 +43298,7 @@
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT210" t="n">
@@ -44327,7 +44327,7 @@
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
@@ -44337,7 +44337,7 @@
       </c>
       <c r="AS215" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT215" t="n">
@@ -45366,7 +45366,7 @@
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
@@ -45376,7 +45376,7 @@
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT220" t="n">
@@ -46405,7 +46405,7 @@
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
@@ -46415,7 +46415,7 @@
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -47834,7 +47834,7 @@
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
@@ -47844,7 +47844,7 @@
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT232" t="n">
@@ -48073,7 +48073,7 @@
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
@@ -48083,7 +48083,7 @@
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT233" t="n">
@@ -49112,7 +49112,7 @@
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
@@ -49122,7 +49122,7 @@
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT238" t="n">
@@ -50151,7 +50151,7 @@
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
@@ -50161,7 +50161,7 @@
       </c>
       <c r="AS243" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT243" t="n">
@@ -51190,7 +51190,7 @@
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
@@ -51200,7 +51200,7 @@
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -52229,7 +52229,7 @@
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
@@ -52239,7 +52239,7 @@
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT253" t="n">
@@ -53268,7 +53268,7 @@
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR258" t="inlineStr">
@@ -53278,7 +53278,7 @@
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT258" t="n">
@@ -54307,7 +54307,7 @@
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR263" t="inlineStr">
@@ -54317,7 +54317,7 @@
       </c>
       <c r="AS263" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT263" t="n">
@@ -55346,7 +55346,7 @@
       </c>
       <c r="AQ268" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR268" t="inlineStr">
@@ -55356,7 +55356,7 @@
       </c>
       <c r="AS268" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT268" t="n">
@@ -56385,7 +56385,7 @@
       </c>
       <c r="AQ273" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR273" t="inlineStr">
@@ -56395,7 +56395,7 @@
       </c>
       <c r="AS273" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT273" t="n">
@@ -57424,7 +57424,7 @@
       </c>
       <c r="AQ278" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr">
@@ -57434,7 +57434,7 @@
       </c>
       <c r="AS278" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT278" t="n">
@@ -58463,7 +58463,7 @@
       </c>
       <c r="AQ283" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR283" t="inlineStr">
@@ -58473,7 +58473,7 @@
       </c>
       <c r="AS283" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT283" t="n">
@@ -59502,7 +59502,7 @@
       </c>
       <c r="AQ288" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR288" t="inlineStr">
@@ -59512,7 +59512,7 @@
       </c>
       <c r="AS288" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_CAMPYLOBACTERIOSIS</t>
+          <t>SER_IS_ECDC_CAMP_ANNUAL</t>
         </is>
       </c>
       <c r="AT288" t="n">

--- a/diseases/d092/1995-1999.xlsx
+++ b/diseases/d092/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -27456,7 +27456,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -29534,7 +29534,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -30573,7 +30573,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -32651,7 +32651,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -33690,7 +33690,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -36397,7 +36397,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -38475,7 +38475,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -39514,7 +39514,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -40553,7 +40553,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -41592,7 +41592,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -42631,7 +42631,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -43670,7 +43670,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -44709,7 +44709,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -45748,7 +45748,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -46787,7 +46787,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -48455,7 +48455,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -49494,7 +49494,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -50533,7 +50533,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -52611,7 +52611,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -53650,7 +53650,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -54689,7 +54689,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -55728,7 +55728,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -56767,7 +56767,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -57806,7 +57806,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -58845,7 +58845,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -59884,7 +59884,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN290" t="b">

--- a/diseases/d092/1995-1999.xlsx
+++ b/diseases/d092/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -27456,7 +27456,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -29534,7 +29534,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -30573,7 +30573,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -32651,7 +32651,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -33690,7 +33690,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -36397,7 +36397,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -38475,7 +38475,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -39514,7 +39514,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -40553,7 +40553,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -41592,7 +41592,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -42631,7 +42631,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -43670,7 +43670,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -44709,7 +44709,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -45748,7 +45748,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -46787,7 +46787,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -48455,7 +48455,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -49494,7 +49494,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -50533,7 +50533,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -52611,7 +52611,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -53650,7 +53650,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -54689,7 +54689,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -55728,7 +55728,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -56767,7 +56767,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -57806,7 +57806,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -58845,7 +58845,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -59884,7 +59884,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN290" t="b">
